--- a/lca estimations/selects1999_lcaresults.xlsx
+++ b/lca estimations/selects1999_lcaresults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\OneDrive\Bureau\master-thesis\lca estimations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\master-thesis\lca estimations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0666C801-7416-4CE0-9C13-5785D05345CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C1C7B2-CB92-4ECC-A35D-0D9C1967EF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{7409AF01-9589-4A5B-B5B8-147D06788643}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="10" xr2:uid="{7409AF01-9589-4A5B-B5B8-147D06788643}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -23,18 +23,30 @@
     <sheet name="Feuil8" sheetId="8" r:id="rId8"/>
     <sheet name="Feuil9" sheetId="9" r:id="rId9"/>
     <sheet name="Feuil10" sheetId="10" r:id="rId10"/>
+    <sheet name="Feuil11" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="483">
   <si>
     <t>selects1999.sav</t>
   </si>
@@ -1499,6 +1511,62 @@
   </si>
   <si>
     <t>Rather old; retired; male; middle income and education; Protestant; German speaking; farmers, craft specialists, skilled and unskilled workers; countryside, middle/small city.</t>
+  </si>
+  <si>
+    <t>Bloc social</t>
+  </si>
+  <si>
+    <t>Groupe socio-politique</t>
+  </si>
+  <si>
+    <t>Demandes politiques</t>
+  </si>
+  <si>
+    <t>Groupes socio-économiques</t>
+  </si>
+  <si>
+    <t>Conservateurs</t>
+  </si>
+  <si>
+    <t>Néolibéraux</t>
+  </si>
+  <si>
+    <t>Artisans, auto-entrepreneurs, employés à faible niveau de qualification et de revenu, retraités. De langue suisse-allemande.</t>
+  </si>
+  <si>
+    <t>Contre les dépenses sociales; pour la taxation des hauts revenus; pour les marchés libres; contre l'immigration et l'intégration européenne</t>
+  </si>
+  <si>
+    <t>Managers et cadres à haut niveau de revenu et d'éducation. Fortement présent en Suisse alémanique</t>
+  </si>
+  <si>
+    <t>Contre les dépenses sociales; contre la taxation des hauts revenus; contre l'intervention de l'État; pour l'immigration et l'intégration européenne</t>
+  </si>
+  <si>
+    <t>Managers et spécialistes socio-culturels à haut niveau d'éducation et de revenu. Pluôt tendance à résider en Romandie</t>
+  </si>
+  <si>
+    <t>Pour augmenter les dépenses sociales et l'intervention de l'État dans l'économie. Pour la taxation des hauts revenus; pour l'immigration et l'intégration européenne.</t>
+  </si>
+  <si>
+    <t>Employés à faible niveau de revenu et d'éducation</t>
+  </si>
+  <si>
+    <t>Libéral-conservateur (dominant)
+Acteurs politiques: UDC, PLR, Le Centre. Principales associations patronales (EconomieSuisse; Usam; UPS)</t>
+  </si>
+  <si>
+    <t>Bloc de gauche
+Acteurs politiques: Parti Socialiste; Unia</t>
+  </si>
+  <si>
+    <t>Pour augmenter les dépenses sociales et l'intervention de l'État dans l'économie. Pour la taxation des hauts revenus; contre l'immigration et l'intégration Européenne</t>
+  </si>
+  <si>
+    <t>Gauche pro-mondialisation</t>
+  </si>
+  <si>
+    <t>Gauche anti-mondialisation</t>
   </si>
 </sst>
 </file>
@@ -1788,7 +1856,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1925,6 +1993,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2739,6 +2813,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2746,7 +2821,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3336,6 +3410,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3343,7 +3418,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3448,7 +3522,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-CH"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3937,6 +4011,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3944,7 +4019,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4533,6 +4607,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4540,7 +4615,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4645,7 +4719,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-CH"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5134,6 +5208,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5141,7 +5216,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5246,7 +5320,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-CH"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5735,6 +5809,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5742,7 +5817,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5847,7 +5921,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-CH"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6336,6 +6410,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6343,7 +6418,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6448,7 +6522,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-CH"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6937,6 +7011,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6944,7 +7019,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7049,7 +7123,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-CH"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -7538,6 +7612,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7545,7 +7620,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12810,9 +12884,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -12850,7 +12924,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -12956,7 +13030,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -13098,7 +13172,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14023,6 +14097,92 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B192F68-EDEF-4113-BAEC-1DD59F9A95FD}">
+  <dimension ref="C3:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="23.7265625" customWidth="1"/>
+    <col min="4" max="4" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E3" t="s">
+        <v>468</v>
+      </c>
+      <c r="F3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="4" spans="3:6" ht="116" x14ac:dyDescent="0.35">
+      <c r="C4" s="55" t="s">
+        <v>478</v>
+      </c>
+      <c r="D4" t="s">
+        <v>469</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>471</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="C5" s="55"/>
+      <c r="D5" t="s">
+        <v>470</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" ht="145" x14ac:dyDescent="0.35">
+      <c r="C6" s="56" t="s">
+        <v>479</v>
+      </c>
+      <c r="D6" t="s">
+        <v>481</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>475</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" ht="145" x14ac:dyDescent="0.35">
+      <c r="C7" s="56"/>
+      <c r="D7" t="s">
+        <v>482</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>477</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>480</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB9709DC-552F-4C6B-9224-EEC8D1F9F04F}">
   <dimension ref="A1:O104"/>
@@ -37354,6 +37514,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B91:M91"/>
+    <mergeCell ref="A105:M105"/>
+    <mergeCell ref="B106:M106"/>
+    <mergeCell ref="A120:M120"/>
+    <mergeCell ref="B121:M121"/>
     <mergeCell ref="A90:M90"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A15:M15"/>
@@ -37366,11 +37531,6 @@
     <mergeCell ref="B61:M61"/>
     <mergeCell ref="A75:M75"/>
     <mergeCell ref="B76:M76"/>
-    <mergeCell ref="B91:M91"/>
-    <mergeCell ref="A105:M105"/>
-    <mergeCell ref="B106:M106"/>
-    <mergeCell ref="A120:M120"/>
-    <mergeCell ref="B121:M121"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -37938,11 +38098,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
@@ -37950,6 +38105,11 @@
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
